--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487689_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487689_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.286199999999999</v>
+        <v>8.962300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0267</v>
+        <v>8.648300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2595</v>
+        <v>0.314</v>
       </c>
       <c r="G2" t="n">
         <v>4.3227</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2306</v>
+        <v>0.4455</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6046</v>
+        <v>0.0171</v>
       </c>
       <c r="U2" t="n">
-        <v>0.374</v>
+        <v>0.4285</v>
       </c>
       <c r="V2" t="n">
         <v>2.4477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2849</v>
+        <v>7.0235</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2924</v>
+        <v>4.813</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9925</v>
+        <v>2.2105</v>
       </c>
       <c r="G3" t="n">
         <v>2.2772</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5704</v>
+        <v>0.309</v>
       </c>
       <c r="T3" t="n">
-        <v>0.729</v>
+        <v>0.2495</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1586</v>
+        <v>0.0595</v>
       </c>
       <c r="V3" t="n">
         <v>4.0492</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1935</v>
+        <v>4.2159</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6569</v>
+        <v>1.8692</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4635</v>
+        <v>2.3467</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7575</v>
+        <v>1.8643</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4644</v>
+        <v>0.9656</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7069</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2814</v>
+        <v>1.0025</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1596</v>
+        <v>0.3707</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1218</v>
+        <v>0.6318</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5238</v>
+        <v>0.8618</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3048</v>
+        <v>0.5948</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8286</v>
+        <v>0.2669</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1632</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.7761</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.6016</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.0935</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.5081</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.9418</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.2239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9612</v>
+        <v>3.1925</v>
       </c>
       <c r="E5" t="n">
-        <v>1.669</v>
+        <v>3.6559</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2922</v>
+        <v>-0.4635</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8643</v>
+        <v>2.7575</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9656</v>
+        <v>3.4644</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8987000000000001</v>
+        <v>-0.7069</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0025</v>
+        <v>3.2814</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3707</v>
+        <v>3.1596</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6318</v>
+        <v>0.1218</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8618</v>
+        <v>-0.5238</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5948</v>
+        <v>0.3048</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2669</v>
+        <v>-0.8286</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.6006</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3634</v>
+        <v>0.0925</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2663</v>
+        <v>0.5081</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2239</v>
+        <v>-0.9418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.805</v>
+        <v>2.366</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7601</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0448</v>
+        <v>2.076</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8092</v>
+        <v>3.1356</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1396</v>
+        <v>4.3195</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3303</v>
+        <v>-1.1839</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1646</v>
+        <v>1.7077</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0834</v>
+        <v>3.6868</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.9792</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.4279</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0562</v>
+        <v>0.6327</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4115</v>
+        <v>0.7952</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0554</v>
+        <v>-0.1278</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7896</v>
+        <v>-0.4475</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2658</v>
+        <v>0.3197</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2239</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1776</v>
+        <v>2.3045</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.171</v>
+        <v>1.2596</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3485</v>
+        <v>1.0448</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1356</v>
+        <v>1.8092</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3195</v>
+        <v>2.1396</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1839</v>
+        <v>-0.3303</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7077</v>
+        <v>1.1646</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6868</v>
+        <v>1.0834</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9792</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4279</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6327</v>
+        <v>1.0562</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7952</v>
+        <v>-0.4115</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3163</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9085</v>
+        <v>0.2891</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.2658</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2239</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0663</v>
+        <v>2.1369</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5745</v>
+        <v>2.637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4918</v>
+        <v>-0.5001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1959</v>
+        <v>-0.5221</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0652</v>
+        <v>0.1219</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1306</v>
+        <v>-0.644</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3249</v>
+        <v>1.3766</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2564</v>
+        <v>0.5191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0684</v>
+        <v>0.8576</v>
       </c>
       <c r="M8" t="n">
-        <v>0.871</v>
+        <v>-1.8987</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1912</v>
+        <v>-0.3971</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0622</v>
+        <v>-1.5015</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7463</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>0.242</v>
+        <v>0.6575</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3623</v>
+        <v>0.053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6046</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1179</v>
+        <v>2.7776</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6119</v>
+        <v>3.3418</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7298</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5025</v>
+        <v>1.9238</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6755</v>
+        <v>1.5955</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.173</v>
+        <v>0.3283</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5221</v>
+        <v>2.1959</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1219</v>
+        <v>1.0652</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.644</v>
+        <v>1.1306</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3766</v>
+        <v>1.3249</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5191</v>
+        <v>1.2564</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8576</v>
+        <v>0.0684</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8987</v>
+        <v>0.871</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3971</v>
+        <v>-0.1912</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5015</v>
+        <v>1.0622</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0231</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9085</v>
+        <v>-0.3413</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9316</v>
+        <v>0.4408</v>
       </c>
       <c r="V9" t="n">
-        <v>2.7776</v>
+        <v>-2.1179</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3418</v>
+        <v>0.6119</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5642</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1309</v>
+        <v>0.3173</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2285</v>
+        <v>1.3497</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3594</v>
+        <v>-1.0324</v>
       </c>
       <c r="G10" t="n">
         <v>0.9036999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.363</v>
+        <v>0.0852</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4834</v>
+        <v>-0.3623</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1205</v>
+        <v>0.4475</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8358</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3379</v>
+        <v>-0.1288</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7206</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3827</v>
+        <v>0.4917</v>
       </c>
       <c r="G11" t="n">
         <v>0.2927</v>
@@ -1312,13 +1312,13 @@
         <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0485</v>
+        <v>0.1607</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0727</v>
+        <v>0.1817</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7973</v>
+        <v>-2.4698</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4559</v>
+        <v>-2.1556</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3415</v>
+        <v>-0.3142</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7403</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1153</v>
+        <v>0.2123</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1875</v>
+        <v>0.2148</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5537</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2901</v>
+        <v>-3.5176</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.249</v>
+        <v>-1.4491</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0412</v>
+        <v>-2.0684</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9085</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5886</v>
+        <v>0.3611</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3039</v>
+        <v>0.1037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2847</v>
+        <v>0.2574</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.721</v>
+        <v>26.3265</v>
       </c>
       <c r="E14" t="n">
-        <v>21.2871</v>
+        <v>21.893</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4334</v>
+        <v>4.433400000000001</v>
       </c>
       <c r="G14" t="n">
         <v>15.3879</v>
@@ -1546,13 +1546,13 @@
         <v>13.5823</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9103</v>
+        <v>3.516099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1386</v>
+        <v>-0.5328999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.049099999999999</v>
+        <v>4.0492</v>
       </c>
       <c r="V14" t="n">
         <v>1.6014</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3368</v>
+        <v>1.2728</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4851</v>
+        <v>0.2849</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8516</v>
+        <v>0.9879</v>
       </c>
       <c r="G15" t="n">
         <v>1.9955</v>
@@ -1624,13 +1624,13 @@
         <v>0.9702</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2243</v>
+        <v>-0.2882</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1806</v>
+        <v>-0.3808</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0437</v>
+        <v>0.0926</v>
       </c>
       <c r="V15" t="n">
         <v>1.506</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3483</v>
+        <v>0.1244</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1881</v>
+        <v>3.3883</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5364</v>
+        <v>-3.2638</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2454</v>
@@ -1702,13 +1702,13 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.079</v>
+        <v>-0.6062</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9556</v>
+        <v>-0.7554</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1233</v>
+        <v>0.1492</v>
       </c>
       <c r="V16" t="n">
         <v>4.5283</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.38</v>
+        <v>-0.0163</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1199</v>
+        <v>0.3201</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5</v>
+        <v>-0.3364</v>
       </c>
       <c r="G17" t="n">
         <v>1.4592</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9094</v>
+        <v>-0.5456</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7145</v>
+        <v>-0.5143</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1949</v>
+        <v>-0.0314</v>
       </c>
       <c r="V17" t="n">
         <v>0.2343</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4817</v>
+        <v>-1.5634</v>
       </c>
       <c r="E18" t="n">
         <v>0.3932</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8749</v>
+        <v>-1.9566</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1138</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6007</v>
+        <v>-0.6825</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4845</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1162</v>
+        <v>-0.1979</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5433</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3119</v>
+        <v>-2.1573</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7018</v>
+        <v>-0.6017</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6101</v>
+        <v>-1.5556</v>
       </c>
       <c r="G19" t="n">
         <v>1.0091</v>
@@ -1936,13 +1936,13 @@
         <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2912</v>
+        <v>-0.1365</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0722</v>
+        <v>0.1267</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4477</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0476</v>
+        <v>-3.5753</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.5676</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9805</v>
+        <v>-3.0078</v>
       </c>
       <c r="G20" t="n">
         <v>-3.8686</v>
@@ -2014,13 +2014,13 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5763</v>
+        <v>0.0485</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1962</v>
+        <v>-0.3043</v>
       </c>
       <c r="U20" t="n">
-        <v>0.38</v>
+        <v>0.3528</v>
       </c>
       <c r="V20" t="n">
         <v>0.2448</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9218</v>
+        <v>-6.4992</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9682</v>
+        <v>-2.18</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9536</v>
+        <v>-4.3192</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.693</v>
+        <v>-3.0013</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2922</v>
+        <v>-3.5006</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4008</v>
+        <v>0.4994</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.225</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.931</v>
+        <v>-0.4984</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2941</v>
+        <v>1.3447</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4679</v>
+        <v>-3.8476</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3612</v>
+        <v>-3.0022</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1067</v>
+        <v>-0.8454</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5821</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0249</v>
+        <v>-0.7248</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2568</v>
+        <v>-0.68</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7681</v>
+        <v>-0.0448</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8358</v>
+        <v>-1.0269</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8358</v>
+        <v>-1.591</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.639</v>
+        <v>-6.622</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0021</v>
+        <v>-2.3686</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6369</v>
+        <v>-4.2534</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9297</v>
+        <v>-5.693</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0038</v>
+        <v>-3.2922</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9258</v>
+        <v>-2.4008</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8912</v>
+        <v>-2.225</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8784</v>
+        <v>-0.931</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0127</v>
+        <v>-1.2941</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0385</v>
+        <v>-3.4679</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1254</v>
+        <v>-2.3612</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9131</v>
+        <v>-1.1067</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2542</v>
+        <v>0.3247</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4229</v>
+        <v>-0.1436</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1687</v>
+        <v>0.4683</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2612</v>
+        <v>-1.8358</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5433</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9274</v>
+        <v>-6.6846</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8807</v>
+        <v>-3.1022</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0467</v>
+        <v>-3.5824</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0013</v>
+        <v>-4.9297</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.5006</v>
+        <v>-3.0038</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4994</v>
+        <v>-1.9258</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8463000000000001</v>
+        <v>-1.8912</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4984</v>
+        <v>-1.8784</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3447</v>
+        <v>-0.0127</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.8476</v>
+        <v>-3.0385</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.0022</v>
+        <v>-1.1254</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8454</v>
+        <v>-1.9131</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7463</v>
+        <v>-0.194</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.153</v>
+        <v>-0.2997</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3807</v>
+        <v>-0.523</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2277</v>
+        <v>0.2232</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0269</v>
+        <v>-1.2612</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.591</v>
+        <v>-1.5433</v>
       </c>
     </row>
     <row r="24">
@@ -2287,7 +2287,7 @@
         <v>-4.4336</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.2875</v>
+        <v>-21.2873</v>
       </c>
       <c r="G24" t="n">
         <v>-15.388</v>
@@ -2296,7 +2296,7 @@
         <v>-15.9995</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6117000000000004</v>
+        <v>0.6117000000000006</v>
       </c>
       <c r="J24" t="n">
         <v>3.2682</v>
@@ -2317,7 +2317,7 @@
         <v>-4.2546</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.821</v>
+        <v>-5.821000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.5824</v>
@@ -2326,16 +2326,16 @@
         <v>7.7613</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9106</v>
+        <v>-2.9103</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.049200000000001</v>
+        <v>-4.0492</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1386</v>
+        <v>1.1387</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.601500000000001</v>
+        <v>-1.6015</v>
       </c>
       <c r="W24" t="n">
         <v>9.9298</v>
